--- a/mock_data/clear_transactions.xlsx
+++ b/mock_data/clear_transactions.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>宁德街门店</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>T0001</t>
+          <t>T5516</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -715,12 +715,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>张路门店</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>T0002</t>
+          <t>T1039</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>批量代发虚拟门店</t>
+          <t>郑州街门店</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>T0003</t>
+          <t>T5880</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>林路门店</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>T0004</t>
+          <t>T9469</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>太原街门店</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>T0006</t>
+          <t>T7735</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>汪路门店</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>T0008</t>
+          <t>T2474</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>西安街门店</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>T0009</t>
+          <t>T0859</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>惠州路门店</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>T0010</t>
+          <t>T3232</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>兰州路门店</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>T0011</t>
+          <t>T5758</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>移动端门店</t>
+          <t>潘路门店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>T0007</t>
+          <t>T8257</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">

--- a/mock_data/clear_transactions.xlsx
+++ b/mock_data/clear_transactions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,12 +561,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F1001</t>
+          <t>F10001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C202605210001</t>
+          <t>C202606000001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>宁德街门店</t>
+          <t>杨路门店</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>T5516</t>
+          <t>T6522</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -601,30 +601,30 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-05-21 09:10:05</t>
+          <t>10:07:05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>100</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,12 +638,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>网银转账</t>
+          <t>支付本月采购货款</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>BAT2026052101</t>
+          <t>BAT2026060001</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -653,22 +653,22 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>REF202605210001</t>
+          <t>REF202606000001</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>ORD202605210001</t>
+          <t>ORD202606000001</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>6214********1001</t>
+          <t>6214********3001</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>上海云杉科技有限公司</t>
+          <t>恩悌网络有限公司</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -683,24 +683,24 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>网银转账</t>
+          <t>支付本月采购货款</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F1002</t>
+          <t>F10002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C202605210002</t>
+          <t>C202606000002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,17 +715,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>张路门店</t>
+          <t>李街门店</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>T1039</t>
+          <t>T1595</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COUNTER</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -735,30 +735,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-05-21 10:20:05</t>
+          <t>11:14:05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>250.5</v>
+        <v>114.7</v>
       </c>
       <c r="M3" t="n">
-        <v>250.5</v>
+        <v>114.7</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>250.5</v>
+        <v>114.7</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>柜面入账</t>
+          <t>小王那笔材料钱</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>BAT2026052101</t>
+          <t>BAT2026060002</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -787,22 +787,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>REF202605210002</t>
+          <t>REF202606000002</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>ORD202605210002</t>
+          <t>ORD202606000002</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>6214********1002</t>
+          <t>6214********3002</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>杭州青禾商贸有限公司</t>
+          <t>易动力信息有限公司</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -817,24 +817,24 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>柜面入账</t>
+          <t>小王那笔材料钱</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F1003</t>
+          <t>F10003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C202605210003</t>
+          <t>C202606000003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,50 +849,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>郑州街门店</t>
+          <t>拉萨街门店</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>T5880</t>
+          <t>T5881</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BATCH</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-05-21 11:30:05</t>
+          <t>12:21:05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>88.8</v>
+        <v>132.05</v>
       </c>
       <c r="M4" t="n">
-        <v>88.8</v>
+        <v>132.05</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>88.8</v>
+        <v>132.05</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -906,12 +906,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>批量代发</t>
+          <t>支付物流运输费用</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>BAT2026052102</t>
+          <t>BAT2026060003</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>REF202605210003</t>
+          <t>REF202606000003</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>ORD202605210003</t>
+          <t>ORD202606000003</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -941,34 +941,34 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6214********1003</t>
+          <t>6214********3003</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>员工代发虚拟户</t>
+          <t>佳禾科技有限公司</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>批量代发</t>
+          <t>支付物流运输费用</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F1004</t>
+          <t>F10004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C202605210004</t>
+          <t>C202606000004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>林路门店</t>
+          <t>王路门店</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>T9469</t>
+          <t>T3261</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CLEARING</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1003,30 +1003,30 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-05-21 13:40:05</t>
+          <t>13:28:05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>295</v>
+        <v>149.4</v>
       </c>
       <c r="M5" t="n">
-        <v>295</v>
+        <v>149.4</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>295</v>
+        <v>149.4</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>清算金额差异</t>
+          <t>供应商催的那笔</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>BAT2026052102</t>
+          <t>BAT2026060004</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1055,22 +1055,22 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>REF202605210004</t>
+          <t>REF202606000004</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>ORD202605210004</t>
+          <t>ORD202606000004</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>6214********1004</t>
+          <t>6214********3004</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>南京北辰供应链有限公司</t>
+          <t>兰金电子网络有限公司</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1085,24 +1085,24 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>清算金额差异</t>
+          <t>供应商催的那笔</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>金额差错样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F1006</t>
+          <t>F10005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C202605210006</t>
+          <t>C202606000005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,17 +1117,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>太原街门店</t>
+          <t>柳州路门店</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>T7735</t>
+          <t>T8959</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CLEARING</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1137,30 +1137,30 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-05-21 15:30:05</t>
+          <t>14:35:05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45</v>
+        <v>166.75</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>166.75</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>45</v>
+        <v>166.75</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,37 +1174,37 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>清算端单边账</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>BAT2026052103</t>
+          <t>BAT2026060005</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>VCH0006</t>
+          <t>VCH0005</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>REF202605210006</t>
+          <t>REF202606000005</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>ORD202605210006</t>
+          <t>ORD202606000005</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>6214********1006</t>
+          <t>6214********3005</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>广州南岭服务有限公司</t>
+          <t>易动力网络有限公司</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>清算端单边账</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>清算端存在银行端缺失</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F1008</t>
+          <t>F10006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C202605210008</t>
+          <t>C202606000006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>汪路门店</t>
+          <t>刘路门店</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>T2474</t>
+          <t>T0524</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-05-21 17:05:05</t>
+          <t>15:42:05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>35.2</v>
+        <v>184.1</v>
       </c>
       <c r="M7" t="n">
-        <v>35.2</v>
+        <v>184.1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>35.2</v>
+        <v>184.1</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1308,27 +1308,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>网银付款</t>
+          <t>门店今天的款补上</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>BAT2026052104</t>
+          <t>BAT2026060006</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>VCH0008</t>
+          <t>VCH0006</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>REF202605210008</t>
+          <t>REF202606000006</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>ORD202605210008</t>
+          <t>ORD202606000006</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1343,34 +1343,34 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6214********1008</t>
+          <t>6214********3006</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>上海浦江物流有限公司</t>
+          <t>联软科技有限公司</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>网银付款</t>
+          <t>门店今天的款补上</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F1009</t>
+          <t>F10007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C202605210009</t>
+          <t>C202606000007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1385,50 +1385,50 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>西安街门店</t>
+          <t>宋街门店</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>T0859</t>
+          <t>T7532</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CLEARING</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-05-21 17:20:05</t>
+          <t>16:49:05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>201.45</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>201.45</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>201.45</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1442,69 +1442,69 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>手续费扣收</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>BAT2026052104</t>
+          <t>BAT2026060007</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>VCH0009</t>
+          <t>VCH0007</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>REF202605210009</t>
+          <t>REF202606000007</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>ORD202605210009</t>
+          <t>ORD202606000007</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>6214********3007</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>凌颖信息科技有限公司</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>6222********0001</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>上海晨星贸易有限公司</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>6214********1009</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>清算服务费虚拟户</t>
+          <t>上海晨星贸易有限公司</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>手续费扣收</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F1010</t>
+          <t>F10008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C202605210010</t>
+          <t>C202606000008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>惠州路门店</t>
+          <t>杨路门店</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>T3232</t>
+          <t>T3782</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1539,30 +1539,30 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-05-21 17:45:05</t>
+          <t>09:56:05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>510</v>
+        <v>218.8</v>
       </c>
       <c r="M9" t="n">
-        <v>510</v>
+        <v>218.8</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>510</v>
+        <v>218.8</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1576,37 +1576,37 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>跨行转账收入</t>
+          <t>小王那笔材料钱</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>BAT2026052105</t>
+          <t>BAT2026060008</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>VCH0010</t>
+          <t>VCH0008</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>REF202605210010</t>
+          <t>REF202606000008</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>ORD202605210010</t>
+          <t>ORD202606000008</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>6214********1010</t>
+          <t>6214********3008</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>无锡云帆材料有限公司</t>
+          <t>思优网络有限公司</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>跨行转账收入</t>
+          <t>小王那笔材料钱</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F1011</t>
+          <t>F10009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C202605210011</t>
+          <t>C202606000009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1653,50 +1653,50 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>兰州路门店</t>
+          <t>刘路门店</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>T5758</t>
+          <t>T7727</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CLEARING</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>REFUND</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-05-21 18:05:05</t>
+          <t>10:03:05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>18.8</v>
+        <v>236.15</v>
       </c>
       <c r="M10" t="n">
-        <v>18.8</v>
+        <v>236.15</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>18.8</v>
+        <v>236.15</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1710,69 +1710,69 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>退款入账</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>BAT2026052105</t>
+          <t>BAT2026060009</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>VCH0011</t>
+          <t>VCH0009</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>REF202605210011</t>
+          <t>REF202606000009</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>ORD202605210011</t>
+          <t>ORD202606000009</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>6214********1011</t>
+          <t>6222********0001</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>上海云杉科技有限公司</t>
+          <t>上海晨星贸易有限公司</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>6222********0001</t>
+          <t>6214********3009</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>上海晨星贸易有限公司</t>
+          <t>国讯科技有限公司</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>退款入账</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F1007</t>
+          <t>F10010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C202605210007</t>
+          <t>C202606000010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>潘路门店</t>
+          <t>合肥街门店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>T8257</t>
+          <t>T8755</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MOBILE_BANKING</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1807,94 +1807,1032 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-05-21 16:30:05</t>
+          <t>11:10:05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>66.59999999999999</v>
+        <v>253.5</v>
       </c>
       <c r="M11" t="n">
-        <v>66.59999999999999</v>
+        <v>253.5</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>上周那单尾款到了</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>BAT2026060010</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>VCH0010</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>REF202606000010</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ORD202606000010</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>6214********3010</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>商软冠联科技有限公司</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>上周那单尾款到了</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>批次正常自动平账样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F10011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C202606000011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>沈阳路门店</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>T4578</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>12:17:05</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>270.85</v>
+      </c>
+      <c r="M12" t="n">
+        <v>270.85</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>270.85</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>收到年度框架协议款</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>BAT2026060011</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>VCH0011</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>REF202606000011</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>ORD202606000011</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>6214********3011</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>立信电子传媒有限公司</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>收到年度框架协议款</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>批次正常自动平账样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F10012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C202606000012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>罗街门店</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>T8241</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13:24:05</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>288.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>288.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>288.2</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>老客户回款一笔</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>BAT2026060012</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>VCH0012</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>REF202606000012</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>ORD202606000012</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>6214********3012</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>东方峻景网络有限公司</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>老客户回款一笔</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>批次正常自动平账样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F12001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C202606010001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>淮安街门店</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>T2605</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>09:00:05</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>128</v>
+      </c>
+      <c r="M14" t="n">
+        <v>128</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>128</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>收到客户合同款项</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>BAT2026060101</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>VCH2001</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>REF202606010001</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>ORD202606010001</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>6214********2001</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>明腾信息有限公司</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>收到客户合同款项</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>批次自动平账哨兵样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F12003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C202606010003</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>覃路门店</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>T9113</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10:10:05</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>295</v>
+      </c>
+      <c r="M15" t="n">
+        <v>295</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>295</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>补付款</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>BAT2026060102</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>VCH2003</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>REF202606010003</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>ORD202606010003</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>6214********2003</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>南京北辰供应链有限公司</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>补付款</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>MVP-1 金额不一致样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F12004</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C202606010004</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>季街门店</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>T0234</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>11:20:05</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="M16" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>正常转账</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>BAT2026052103</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>VCH0007</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>REF202605210007</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>ORD202605210007</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>6214********1007</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>支付本月采购货款</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>BAT2026060102</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>VCH2004</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>REF202606010004</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ORD202606010004</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>6214********2004</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>宁波星河电子有限公司</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>6222********0001</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>上海晨星贸易有限公司</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>正常转账</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>正常平账样例</t>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>支付本月采购货款</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>MVP-1 摘要客户名不一致样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>F12005</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C202606010005</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>孔路门店</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>T1315</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>13:30:05</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>72</v>
+      </c>
+      <c r="M17" t="n">
+        <v>72</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>72</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>代收代付</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>BAT2026060103</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>VCH2005</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>REF202606010005</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>ORD202606010005</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>6214********2005</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>广州南岭服务有限公司</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>代收代付</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>MVP-1 企业有银行无样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>F12007</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>C202606010007</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>海门路门店</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>T1197</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>15:00:05</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="M18" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>临时款项</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>BAT2026060104</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>VCH2007</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>REF202606010007</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ORD202606010007</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>6214********2007</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>杭州青禾商贸有限公司</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>临时款项</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>MVP-1 疑似重复入账样例</t>
         </is>
       </c>
     </row>

--- a/mock_data/clear_transactions.xlsx
+++ b/mock_data/clear_transactions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,12 +561,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F1001</t>
+          <t>F10001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C202605210001</t>
+          <t>C202606000001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>杨路门店</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>T0001</t>
+          <t>T6522</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -601,30 +601,30 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-05-21 09:10:05</t>
+          <t>10:07:05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>100</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -638,12 +638,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>网银转账</t>
+          <t>支付本月采购货款</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>BAT2026052101</t>
+          <t>BAT2026060001</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -653,22 +653,22 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>REF202605210001</t>
+          <t>REF202606000001</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>ORD202605210001</t>
+          <t>ORD202606000001</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>6214********1001</t>
+          <t>6214********3001</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>上海云杉科技有限公司</t>
+          <t>恩悌网络有限公司</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -683,24 +683,24 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>网银转账</t>
+          <t>支付本月采购货款</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F1002</t>
+          <t>F10002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C202605210002</t>
+          <t>C202606000002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,17 +715,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>李街门店</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>T0002</t>
+          <t>T1595</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COUNTER</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -735,30 +735,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-05-21 10:20:05</t>
+          <t>11:14:05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>250.5</v>
+        <v>114.7</v>
       </c>
       <c r="M3" t="n">
-        <v>250.5</v>
+        <v>114.7</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>250.5</v>
+        <v>114.7</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>柜面入账</t>
+          <t>小王那笔材料钱</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>BAT2026052101</t>
+          <t>BAT2026060002</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -787,22 +787,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>REF202605210002</t>
+          <t>REF202606000002</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>ORD202605210002</t>
+          <t>ORD202606000002</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>6214********1002</t>
+          <t>6214********3002</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>杭州青禾商贸有限公司</t>
+          <t>易动力信息有限公司</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -817,24 +817,24 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>柜面入账</t>
+          <t>小王那笔材料钱</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F1003</t>
+          <t>F10003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C202605210003</t>
+          <t>C202606000003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,50 +849,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>批量代发虚拟门店</t>
+          <t>拉萨街门店</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>T0003</t>
+          <t>T5881</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BATCH</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-05-21 11:30:05</t>
+          <t>12:21:05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>88.8</v>
+        <v>132.05</v>
       </c>
       <c r="M4" t="n">
-        <v>88.8</v>
+        <v>132.05</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>88.8</v>
+        <v>132.05</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -906,12 +906,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>批量代发</t>
+          <t>支付物流运输费用</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>BAT2026052102</t>
+          <t>BAT2026060003</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>REF202605210003</t>
+          <t>REF202606000003</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>ORD202605210003</t>
+          <t>ORD202606000003</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -941,34 +941,34 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6214********1003</t>
+          <t>6214********3003</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>员工代发虚拟户</t>
+          <t>佳禾科技有限公司</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>批量代发</t>
+          <t>支付物流运输费用</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F1004</t>
+          <t>F10004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C202605210004</t>
+          <t>C202606000004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>王路门店</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>T0004</t>
+          <t>T3261</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CLEARING</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1003,30 +1003,30 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-05-21 13:40:05</t>
+          <t>13:28:05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>295</v>
+        <v>149.4</v>
       </c>
       <c r="M5" t="n">
-        <v>295</v>
+        <v>149.4</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>295</v>
+        <v>149.4</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>清算金额差异</t>
+          <t>供应商催的那笔</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>BAT2026052102</t>
+          <t>BAT2026060004</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1055,22 +1055,22 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>REF202605210004</t>
+          <t>REF202606000004</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>ORD202605210004</t>
+          <t>ORD202606000004</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>6214********1004</t>
+          <t>6214********3004</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>南京北辰供应链有限公司</t>
+          <t>兰金电子网络有限公司</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1085,24 +1085,24 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>清算金额差异</t>
+          <t>供应商催的那笔</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>金额差错样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F1006</t>
+          <t>F10005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C202605210006</t>
+          <t>C202606000005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,17 +1117,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>柳州路门店</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>T0006</t>
+          <t>T8959</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CLEARING</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1137,30 +1137,30 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-05-21 15:30:05</t>
+          <t>14:35:05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45</v>
+        <v>166.75</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>166.75</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>45</v>
+        <v>166.75</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,37 +1174,37 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>清算端单边账</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>BAT2026052103</t>
+          <t>BAT2026060005</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>VCH0006</t>
+          <t>VCH0005</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>REF202605210006</t>
+          <t>REF202606000005</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>ORD202605210006</t>
+          <t>ORD202606000005</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>6214********1006</t>
+          <t>6214********3005</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>广州南岭服务有限公司</t>
+          <t>易动力网络有限公司</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>清算端单边账</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>清算端存在银行端缺失</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F1008</t>
+          <t>F10006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C202605210008</t>
+          <t>C202606000006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>刘路门店</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>T0008</t>
+          <t>T0524</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-05-21 17:05:05</t>
+          <t>15:42:05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>35.2</v>
+        <v>184.1</v>
       </c>
       <c r="M7" t="n">
-        <v>35.2</v>
+        <v>184.1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>35.2</v>
+        <v>184.1</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1308,27 +1308,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>网银付款</t>
+          <t>门店今天的款补上</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>BAT2026052104</t>
+          <t>BAT2026060006</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>VCH0008</t>
+          <t>VCH0006</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>REF202605210008</t>
+          <t>REF202606000006</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>ORD202605210008</t>
+          <t>ORD202606000006</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1343,34 +1343,34 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6214********1008</t>
+          <t>6214********3006</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>上海浦江物流有限公司</t>
+          <t>联软科技有限公司</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>网银付款</t>
+          <t>门店今天的款补上</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F1009</t>
+          <t>F10007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C202605210009</t>
+          <t>C202606000007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1385,50 +1385,50 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>宋街门店</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>T0009</t>
+          <t>T7532</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CLEARING</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-05-21 17:20:05</t>
+          <t>16:49:05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>201.45</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>201.45</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>201.45</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1442,69 +1442,69 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>手续费扣收</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>BAT2026052104</t>
+          <t>BAT2026060007</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>VCH0009</t>
+          <t>VCH0007</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>REF202605210009</t>
+          <t>REF202606000007</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>ORD202605210009</t>
+          <t>ORD202606000007</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>6214********3007</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>凌颖信息科技有限公司</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>6222********0001</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>上海晨星贸易有限公司</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>6214********1009</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>清算服务费虚拟户</t>
+          <t>上海晨星贸易有限公司</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>手续费扣收</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F1010</t>
+          <t>F10008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C202605210010</t>
+          <t>C202606000008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1519,12 +1519,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>杨路门店</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>T0010</t>
+          <t>T3782</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1539,30 +1539,30 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-05-21 17:45:05</t>
+          <t>09:56:05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>510</v>
+        <v>218.8</v>
       </c>
       <c r="M9" t="n">
-        <v>510</v>
+        <v>218.8</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>510</v>
+        <v>218.8</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1576,37 +1576,37 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>跨行转账收入</t>
+          <t>小王那笔材料钱</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>BAT2026052105</t>
+          <t>BAT2026060008</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>VCH0010</t>
+          <t>VCH0008</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>REF202605210010</t>
+          <t>REF202606000008</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>ORD202605210010</t>
+          <t>ORD202606000008</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>6214********1010</t>
+          <t>6214********3008</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>无锡云帆材料有限公司</t>
+          <t>思优网络有限公司</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>跨行转账收入</t>
+          <t>小王那笔材料钱</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F1011</t>
+          <t>F10009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C202605210011</t>
+          <t>C202606000009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1653,50 +1653,50 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>总部直营网点</t>
+          <t>刘路门店</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>T0011</t>
+          <t>T7727</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CLEARING</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>REFUND</t>
+          <t>PAYMENT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-05-21 18:05:05</t>
+          <t>10:03:05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>18.8</v>
+        <v>236.15</v>
       </c>
       <c r="M10" t="n">
-        <v>18.8</v>
+        <v>236.15</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>18.8</v>
+        <v>236.15</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1710,69 +1710,69 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>退款入账</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>BAT2026052105</t>
+          <t>BAT2026060009</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>VCH0011</t>
+          <t>VCH0009</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>REF202605210011</t>
+          <t>REF202606000009</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>ORD202605210011</t>
+          <t>ORD202606000009</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>6214********1011</t>
+          <t>6222********0001</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>上海云杉科技有限公司</t>
+          <t>上海晨星贸易有限公司</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>6222********0001</t>
+          <t>6214********3009</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>上海晨星贸易有限公司</t>
+          <t>国讯科技有限公司</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>退款入账</t>
+          <t>收到客户合同款项</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>正常平账样例</t>
+          <t>批次正常自动平账样例</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F1007</t>
+          <t>F10010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C202605210007</t>
+          <t>C202606000010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>移动端门店</t>
+          <t>合肥街门店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>T0007</t>
+          <t>T8755</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MOBILE_BANKING</t>
+          <t>ONLINE_BANKING</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1807,94 +1807,1032 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-05-21 16:30:05</t>
+          <t>11:10:05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>66.59999999999999</v>
+        <v>253.5</v>
       </c>
       <c r="M11" t="n">
-        <v>66.59999999999999</v>
+        <v>253.5</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>上周那单尾款到了</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>BAT2026060010</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>VCH0010</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>REF202606000010</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ORD202606000010</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>6214********3010</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>商软冠联科技有限公司</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>上周那单尾款到了</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>批次正常自动平账样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F10011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C202606000011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>沈阳路门店</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>T4578</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>12:17:05</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>270.85</v>
+      </c>
+      <c r="M12" t="n">
+        <v>270.85</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>270.85</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>收到年度框架协议款</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>BAT2026060011</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>VCH0011</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>REF202606000011</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>ORD202606000011</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>6214********3011</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>立信电子传媒有限公司</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>收到年度框架协议款</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>批次正常自动平账样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F10012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C202606000012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>罗街门店</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>T8241</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13:24:05</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>288.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>288.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>288.2</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>老客户回款一笔</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>BAT2026060012</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>VCH0012</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>REF202606000012</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>ORD202606000012</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>6214********3012</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>东方峻景网络有限公司</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>老客户回款一笔</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>批次正常自动平账样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F12001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C202606010001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>淮安街门店</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>T2605</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>09:00:05</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>128</v>
+      </c>
+      <c r="M14" t="n">
+        <v>128</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>128</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>收到客户合同款项</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>BAT2026060101</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>VCH2001</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>REF202606010001</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>ORD202606010001</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>6214********2001</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>明腾信息有限公司</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>收到客户合同款项</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>批次自动平账哨兵样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F12003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C202606010003</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>覃路门店</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>T9113</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10:10:05</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>295</v>
+      </c>
+      <c r="M15" t="n">
+        <v>295</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>295</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>补付款</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>BAT2026060102</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>VCH2003</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>REF202606010003</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>ORD202606010003</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>6214********2003</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>南京北辰供应链有限公司</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>补付款</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>MVP-1 金额不一致样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F12004</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C202606010004</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>季街门店</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>T0234</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>11:20:05</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="M16" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>正常转账</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>BAT2026052103</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>VCH0007</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>REF202605210007</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>ORD202605210007</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>6214********1007</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>支付本月采购货款</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>BAT2026060102</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>VCH2004</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>REF202606010004</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ORD202606010004</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>6214********2004</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>宁波星河电子有限公司</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>6222********0001</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>上海晨星贸易有限公司</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>正常转账</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>正常平账样例</t>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>支付本月采购货款</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>MVP-1 摘要客户名不一致样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>F12005</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C202606010005</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>孔路门店</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>T1315</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>13:30:05</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>72</v>
+      </c>
+      <c r="M17" t="n">
+        <v>72</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>72</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>代收代付</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>BAT2026060103</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>VCH2005</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>REF202606010005</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>ORD202606010005</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>6214********2005</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>广州南岭服务有限公司</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>代收代付</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>MVP-1 企业有银行无样例</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>F12007</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>C202606010007</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M1000001</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>海门路门店</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>T1197</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ONLINE_BANKING</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PAYMENT</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>15:00:05</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="M18" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>临时款项</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>BAT2026060104</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>VCH2007</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>REF202606010007</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ORD202606010007</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>6214********2007</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>杭州青禾商贸有限公司</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>6222********0001</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>上海晨星贸易有限公司</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>临时款项</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>MVP-1 疑似重复入账样例</t>
         </is>
       </c>
     </row>
